--- a/results/reliability_eval/Llama-3-8B_P101_sample_15_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P101_sample_15_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5037788331071913</v>
+        <v>0.4901539522058824</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3362739839583877</v>
+        <v>0.3137567011427013</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5037788331071913</v>
+        <v>0.4901539522058824</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3362739839583877</v>
+        <v>0.3137567011427013</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5029149706015378</v>
+        <v>0.5095611213235294</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3469024472300921</v>
+        <v>0.3348676042895873</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9956580732700135</v>
+        <v>0.9872702205882353</v>
       </c>
       <c r="H2" t="n">
-        <v>0.98927875874372</v>
+        <v>0.9706182754979495</v>
       </c>
       <c r="I2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
